--- a/data/descargas/corte_caja.xlsx
+++ b/data/descargas/corte_caja.xlsx
@@ -573,7 +573,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reporte generado: 01-01-2026 07:11 a. m. </t>
+          <t xml:space="preserve">Reporte generado: 01-01-2026 07:35 a. m. </t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>

--- a/data/descargas/corte_caja.xlsx
+++ b/data/descargas/corte_caja.xlsx
@@ -573,7 +573,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reporte generado: 01-01-2026 07:35 a. m. </t>
+          <t>Reporte generado: 01-01-2026 03:22 p. m.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>

--- a/data/descargas/corte_caja.xlsx
+++ b/data/descargas/corte_caja.xlsx
@@ -573,7 +573,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reporte generado: 01-02-2026 07:50 a. m. </t>
+          <t>Reporte generado: 01-02-2026 03:25 p. m.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>

--- a/data/descargas/corte_caja.xlsx
+++ b/data/descargas/corte_caja.xlsx
@@ -573,7 +573,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reporte generado: 01-03-2026 07:20 a. m. </t>
+          <t xml:space="preserve">Reporte generado: 01-03-2026 07:47 a. m. </t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>

--- a/data/descargas/corte_caja.xlsx
+++ b/data/descargas/corte_caja.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,44 +549,156 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>IXTA260006536</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2.622052275972001e+19</v>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>$ .00</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>CLAUDIA DANIELA JIMENEZ SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>499</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>01-03-26</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>28-03-26</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>RECURRENTE LINEA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Jose Luis  Gonzalez</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reporte generado: 01-03-2026 07:47 a. m. </t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LPAZ260005679</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2.621052275971e+19</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>02:02</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ARIANA SCARLETT  ROSENDO VILLALOBOS</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>499</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>01-03-26</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>28-03-26</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>RECURRENTE LINEA</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Juan Jesus Palafox</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>$ 998.00</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Reporte generado: 01-03-2026 03:24 p. m.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/corte_caja.xlsx
+++ b/data/descargas/corte_caja.xlsx
@@ -552,7 +552,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DEL 01-07-2026 AL 22-07-2026</t>
+          <t>DEL 01-07-2026 AL 23-07-2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -563,7 +563,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>$ 14,250,383.20</t>
+          <t>$ 14,866,883.00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -577,7 +577,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Reporte generado: 22-07-2026 04:22 p. m.</t>
+          <t>Reporte generado: 23-07-2026 04:27 p. m.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
